--- a/Employee_Reports_wi52/Roby Chua Malinao Q0613.xlsx
+++ b/Employee_Reports_wi52/Roby Chua Malinao Q0613.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1167,11 +1167,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1216,11 +1216,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1231,78 +1231,78 @@
       <c r="K16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -1327,11 +1327,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1364,11 +1364,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
